--- a/services/autopts_report/report_2026_03_14_00_01_42.xlsx
+++ b/services/autopts_report/report_2026_03_14_00_01_42.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="255">
-  <si>
-    <t>AutoPTS Report: 2026-03-14 00:34</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="202">
+  <si>
+    <t>AutoPTS Report: 2026-03-14 00:40</t>
   </si>
   <si>
     <t>Test Case</t>
@@ -49,9 +49,6 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>DIS_SR_SGGIT_CHA_BV_01_C_2026_03_14_00_03_23.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Manufacturer Name String</t>
   </si>
   <si>
@@ -64,9 +61,6 @@
     <t>DIS/SR/SGGIT/CHA/BV-02-C</t>
   </si>
   <si>
-    <t>DIS_SR_SGGIT_CHA_BV_02_C_2026_03_14_00_03_42.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Model Number String</t>
   </si>
   <si>
@@ -76,9 +70,6 @@
     <t>DIS/SR/SGGIT/CHA/BV-03-C</t>
   </si>
   <si>
-    <t>DIS_SR_SGGIT_CHA_BV_03_C_2026_03_14_00_04_00.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Serial Number String</t>
   </si>
   <si>
@@ -88,9 +79,6 @@
     <t>DIS/SR/SGGIT/CHA/BV-04-C</t>
   </si>
   <si>
-    <t>DIS_SR_SGGIT_CHA_BV_04_C_2026_03_14_00_04_20.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Hardware Revision String</t>
   </si>
   <si>
@@ -100,9 +88,6 @@
     <t>DIS/SR/SGGIT/CHA/BV-05-C</t>
   </si>
   <si>
-    <t>DIS_SR_SGGIT_CHA_BV_05_C_2026_03_14_00_04_39.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Firmware Revision String</t>
   </si>
   <si>
@@ -115,9 +100,6 @@
     <t>DIS/SR/SGGIT/CHA/BV-06-C</t>
   </si>
   <si>
-    <t>DIS_SR_SGGIT_CHA_BV_06_C_2026_03_14_00_04_58.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Software Revision String</t>
   </si>
   <si>
@@ -127,9 +109,6 @@
     <t>DIS/SR/SGGIT/CHA/BV-09-C</t>
   </si>
   <si>
-    <t>DIS_SR_SGGIT_CHA_BV_09_C_2026_03_14_00_05_17.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - PnP ID</t>
   </si>
   <si>
@@ -139,9 +118,6 @@
     <t>DIS/SR/SGGIT/SER/BV-01-C</t>
   </si>
   <si>
-    <t>DIS_SR_SGGIT_SER_BV_01_C_2026_03_14_00_03_03.xml</t>
-  </si>
-  <si>
     <t>Service GGIT - Device Information as a Primary Service</t>
   </si>
   <si>
@@ -151,9 +127,6 @@
     <t>OTS/SR/CON/BV-01-C</t>
   </si>
   <si>
-    <t>OTS_SR_CON_BV_01_C_2026_03_14_00_13_05.xml</t>
-  </si>
-  <si>
     <t>Configure Indication - OACP</t>
   </si>
   <si>
@@ -166,9 +139,6 @@
     <t>OTS/SR/CON/BV-02-C</t>
   </si>
   <si>
-    <t>OTS_SR_CON_BV_02_C_2026_03_14_00_13_28.xml</t>
-  </si>
-  <si>
     <t>Configure Indication - OLCP</t>
   </si>
   <si>
@@ -193,9 +163,6 @@
     <t>OTS/SR/CR/BV-01-C</t>
   </si>
   <si>
-    <t>OTS_SR_CR_BV_01_C_2026_03_14_00_09_25.xml</t>
-  </si>
-  <si>
     <t>Characteristic Read - OTS Feature</t>
   </si>
   <si>
@@ -208,9 +175,6 @@
     <t>OTS/SR/CR/BV-02-C</t>
   </si>
   <si>
-    <t>OTS_SR_CR_BV_02_C_2026_03_14_00_09_50.xml</t>
-  </si>
-  <si>
     <t>Characteristic Read - Object Name</t>
   </si>
   <si>
@@ -220,9 +184,6 @@
     <t>OTS/SR/CR/BV-03-C</t>
   </si>
   <si>
-    <t>OTS_SR_CR_BV_03_C_2026_03_14_00_10_14.xml</t>
-  </si>
-  <si>
     <t>Characteristic Read - Object Type</t>
   </si>
   <si>
@@ -232,9 +193,6 @@
     <t>OTS/SR/CR/BV-04-C</t>
   </si>
   <si>
-    <t>OTS_SR_CR_BV_04_C_2026_03_14_00_10_38.xml</t>
-  </si>
-  <si>
     <t>Characteristic Read - Object Size</t>
   </si>
   <si>
@@ -244,9 +202,6 @@
     <t>OTS/SR/CR/BV-07-C</t>
   </si>
   <si>
-    <t>OTS_SR_CR_BV_07_C_2026_03_14_00_11_03.xml</t>
-  </si>
-  <si>
     <t>Characteristic Read - Object ID</t>
   </si>
   <si>
@@ -256,9 +211,6 @@
     <t>OTS/SR/CR/BV-08-C</t>
   </si>
   <si>
-    <t>OTS_SR_CR_BV_08_C_2026_03_14_00_11_27.xml</t>
-  </si>
-  <si>
     <t>Characteristic Read - Object Properties</t>
   </si>
   <si>
@@ -268,9 +220,6 @@
     <t>OTS/SR/CRL/BV-01-C</t>
   </si>
   <si>
-    <t>OTS_SR_CRL_BV_01_C_2026_03_14_00_11_51.xml</t>
-  </si>
-  <si>
     <t>Characteristic Read Long - Object Name</t>
   </si>
   <si>
@@ -280,9 +229,6 @@
     <t>OTS/SR/CW/BV-01-C</t>
   </si>
   <si>
-    <t>OTS_SR_CW_BV_01_C_2026_03_14_00_12_15.xml</t>
-  </si>
-  <si>
     <t>Characteristic Write - Object Name</t>
   </si>
   <si>
@@ -292,18 +238,12 @@
     <t>OTS/SR/CWL/BV-01-C</t>
   </si>
   <si>
-    <t>OTS_SR_CWL_BV_01_C_2026_03_14_00_12_39.xml</t>
-  </si>
-  <si>
     <t>Characteristic Write Long - Object Name</t>
   </si>
   <si>
     <t>OTS/SR/DLO/BV-01-C</t>
   </si>
   <si>
-    <t>OTS_SR_DLO_BV_01_C_2026_03_14_00_33_08.xml</t>
-  </si>
-  <si>
     <t>Generation of Directory Listing Object</t>
   </si>
   <si>
@@ -316,9 +256,6 @@
     <t>OTS/SR/OAE/BI-01-C</t>
   </si>
   <si>
-    <t>OTS_SR_OAE_BI_01_C_2026_03_14_00_18_54.xml</t>
-  </si>
-  <si>
     <t>OACP - Op Code Not Supported</t>
   </si>
   <si>
@@ -331,9 +268,6 @@
     <t>OTS/SR/OAE/BI-03-C</t>
   </si>
   <si>
-    <t>OTS_SR_OAE_BI_03_C_2026_03_14_00_19_18.xml</t>
-  </si>
-  <si>
     <t>OACP - Channel Unavailable - Read</t>
   </si>
   <si>
@@ -343,9 +277,6 @@
     <t>OTS/SR/OAE/BI-04-C</t>
   </si>
   <si>
-    <t>OTS_SR_OAE_BI_04_C_2026_03_14_00_19_45.xml</t>
-  </si>
-  <si>
     <t>OACP - Channel Unavailable - Write</t>
   </si>
   <si>
@@ -358,9 +289,6 @@
     <t>OTS/SR/OAE/BI-05-C</t>
   </si>
   <si>
-    <t>OTS_SR_OAE_BI_05_C_2026_03_14_00_20_13.xml</t>
-  </si>
-  <si>
     <t>OACP - Unsupported Type</t>
   </si>
   <si>
@@ -370,9 +298,6 @@
     <t>OTS/SR/OAE/BI-06-C</t>
   </si>
   <si>
-    <t>OTS_SR_OAE_BI_06_C_2026_03_14_00_20_43.xml</t>
-  </si>
-  <si>
     <t>OACP - Delete Not Permitted</t>
   </si>
   <si>
@@ -382,9 +307,6 @@
     <t>OTS/SR/OAE/BI-08-C</t>
   </si>
   <si>
-    <t>OTS_SR_OAE_BI_08_C_2026_03_14_00_21_10.xml</t>
-  </si>
-  <si>
     <t>OACP - Read Not Permitted</t>
   </si>
   <si>
@@ -394,9 +316,6 @@
     <t>OTS/SR/OAE/BI-09-C</t>
   </si>
   <si>
-    <t>OTS_SR_OAE_BI_09_C_2026_03_14_00_21_38.xml</t>
-  </si>
-  <si>
     <t>OACP - Write Not Permitted</t>
   </si>
   <si>
@@ -406,9 +325,6 @@
     <t>OTS/SR/OAE/BI-12-C</t>
   </si>
   <si>
-    <t>OTS_SR_OAE_BI_12_C_2026_03_14_00_22_05.xml</t>
-  </si>
-  <si>
     <t>OACP - Client Characteristic Configuration Descriptor Improperly Configured</t>
   </si>
   <si>
@@ -418,9 +334,6 @@
     <t>OTS/SR/OAE/BI-13-C</t>
   </si>
   <si>
-    <t>OTS_SR_OAE_BI_13_C_2026_03_14_00_22_30.xml</t>
-  </si>
-  <si>
     <t>OACP - Invalid Parameter</t>
   </si>
   <si>
@@ -430,9 +343,6 @@
     <t>OTS/SR/OASP/BV-01-C</t>
   </si>
   <si>
-    <t>OTS_SR_OASP_BV_01_C_2026_03_14_00_15_14.xml</t>
-  </si>
-  <si>
     <t>OACP - Create</t>
   </si>
   <si>
@@ -445,9 +355,6 @@
     <t>OTS/SR/OASP/BV-02-C</t>
   </si>
   <si>
-    <t>OTS_SR_OASP_BV_02_C_2026_03_14_00_15_42.xml</t>
-  </si>
-  <si>
     <t>OACP - Delete</t>
   </si>
   <si>
@@ -457,9 +364,6 @@
     <t>OTS/SR/OASP/BV-03-C</t>
   </si>
   <si>
-    <t>OTS_SR_OASP_BV_03_C_2026_03_14_00_16_11.xml</t>
-  </si>
-  <si>
     <t>OACP - Calculate Checksum</t>
   </si>
   <si>
@@ -469,9 +373,6 @@
     <t>OTS/SR/OASP/BV-04-C</t>
   </si>
   <si>
-    <t>OTS_SR_OASP_BV_04_C_2026_03_14_00_16_46.xml</t>
-  </si>
-  <si>
     <t>OACP - Read - Entire Object</t>
   </si>
   <si>
@@ -481,9 +382,6 @@
     <t>OTS/SR/OASP/BV-05-C</t>
   </si>
   <si>
-    <t>OTS_SR_OASP_BV_05_C_2026_03_14_00_17_14.xml</t>
-  </si>
-  <si>
     <t>OACP - Read - Part of Object</t>
   </si>
   <si>
@@ -493,9 +391,6 @@
     <t>OTS/SR/OASP/BV-06-C</t>
   </si>
   <si>
-    <t>OTS_SR_OASP_BV_06_C_2026_03_14_00_17_44.xml</t>
-  </si>
-  <si>
     <t>OACP - Write - Entire Object</t>
   </si>
   <si>
@@ -505,9 +400,6 @@
     <t>OTS/SR/OASP/BV-07-C</t>
   </si>
   <si>
-    <t>OTS_SR_OASP_BV_07_C_2026_03_14_00_18_20.xml</t>
-  </si>
-  <si>
     <t>OACP - Write - Patching an Object</t>
   </si>
   <si>
@@ -526,9 +418,6 @@
     <t>OTS/SR/OLE/BI-01-C</t>
   </si>
   <si>
-    <t>OTS_SR_OLE_BI_01_C_2026_03_14_00_23_56.xml</t>
-  </si>
-  <si>
     <t>OLCP - Op Code Not Supported</t>
   </si>
   <si>
@@ -541,9 +430,6 @@
     <t>OTS/SR/OLE/BI-03-C</t>
   </si>
   <si>
-    <t>OTS_SR_OLE_BI_03_C_2026_03_14_00_33_53.xml</t>
-  </si>
-  <si>
     <t>OLCP - No Object</t>
   </si>
   <si>
@@ -556,9 +442,6 @@
     <t>OTS/SR/OLE/BI-04-C</t>
   </si>
   <si>
-    <t>OTS_SR_OLE_BI_04_C_2026_03_14_00_24_21.xml</t>
-  </si>
-  <si>
     <t>OLCP - Object ID Not Found</t>
   </si>
   <si>
@@ -568,9 +451,6 @@
     <t>OTS/SR/OLE/BI-05-C</t>
   </si>
   <si>
-    <t>OTS_SR_OLE_BI_05_C_2026_03_14_00_24_46.xml</t>
-  </si>
-  <si>
     <t>OLCP - Client Characteristic Configuration Descriptor Improperly Configured</t>
   </si>
   <si>
@@ -580,9 +460,6 @@
     <t>OTS/SR/OLSP/BV-01-C</t>
   </si>
   <si>
-    <t>OTS_SR_OLSP_BV_01_C_2026_03_14_00_22_57.xml</t>
-  </si>
-  <si>
     <t>OLCP - First, Last, Previous and Next</t>
   </si>
   <si>
@@ -592,27 +469,18 @@
     <t>OTS/SR/OLSP/BV-02-C</t>
   </si>
   <si>
-    <t>OTS_SR_OLSP_BV_02_C_2026_03_14_00_23_25.xml</t>
-  </si>
-  <si>
     <t>OLCP - Go To</t>
   </si>
   <si>
     <t>OTS/SR/OME/BI-01-C</t>
   </si>
   <si>
-    <t>OTS_SR_OME_BI_01_C_2026_03_14_00_25_12.xml</t>
-  </si>
-  <si>
     <t>Object Metadata - Object Name Already Exists</t>
   </si>
   <si>
     <t>OTS/SR/OTD/BI-01-C</t>
   </si>
   <si>
-    <t>OTS_SR_OTD_BI_01_C_2026_03_14_00_27_03.xml</t>
-  </si>
-  <si>
     <t>Malformed Object - Deleted when Connection Terminated</t>
   </si>
   <si>
@@ -652,9 +520,6 @@
     <t>OTS/SR/SGGIT/CHA/BV-01-C</t>
   </si>
   <si>
-    <t>OTS_SR_SGGIT_CHA_BV_01_C_2026_03_14_00_05_58.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - OTS Feature</t>
   </si>
   <si>
@@ -667,9 +532,6 @@
     <t>OTS/SR/SGGIT/CHA/BV-03-C</t>
   </si>
   <si>
-    <t>OTS_SR_SGGIT_CHA_BV_03_C_2026_03_14_00_06_22.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Object Name - Write</t>
   </si>
   <si>
@@ -679,9 +541,6 @@
     <t>OTS/SR/SGGIT/CHA/BV-04-C</t>
   </si>
   <si>
-    <t>OTS_SR_SGGIT_CHA_BV_04_C_2026_03_14_00_06_45.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Object Type</t>
   </si>
   <si>
@@ -691,9 +550,6 @@
     <t>OTS/SR/SGGIT/CHA/BV-05-C</t>
   </si>
   <si>
-    <t>OTS_SR_SGGIT_CHA_BV_05_C_2026_03_14_00_07_08.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Object Size</t>
   </si>
   <si>
@@ -703,9 +559,6 @@
     <t>OTS/SR/SGGIT/CHA/BV-10-C</t>
   </si>
   <si>
-    <t>OTS_SR_SGGIT_CHA_BV_10_C_2026_03_14_00_07_31.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Object ID</t>
   </si>
   <si>
@@ -715,9 +568,6 @@
     <t>OTS/SR/SGGIT/CHA/BV-11-C</t>
   </si>
   <si>
-    <t>OTS_SR_SGGIT_CHA_BV_11_C_2026_03_14_00_07_54.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Object Properties</t>
   </si>
   <si>
@@ -727,9 +577,6 @@
     <t>OTS/SR/SGGIT/CHA/BV-13-C</t>
   </si>
   <si>
-    <t>OTS_SR_SGGIT_CHA_BV_13_C_2026_03_14_00_08_16.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Object Action Control Point</t>
   </si>
   <si>
@@ -739,9 +586,6 @@
     <t>OTS/SR/SGGIT/CHA/BV-14-C</t>
   </si>
   <si>
-    <t>OTS_SR_SGGIT_CHA_BV_14_C_2026_03_14_00_08_40.xml</t>
-  </si>
-  <si>
     <t>Characteristic GGIT - Object List Control Point</t>
   </si>
   <si>
@@ -758,9 +602,6 @@
   </si>
   <si>
     <t>OTS/SR/SGGIT/SER/BV-01-C</t>
-  </si>
-  <si>
-    <t>OTS_SR_SGGIT_SER_BV_01_C_2026_03_14_00_05_36.xml</t>
   </si>
   <si>
     <t>Service GGIT - Object Transfer</t>
@@ -1286,7 +1127,7 @@
         <v>8</v>
       </c>
       <c r="K3" t="s">
-        <v>250</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1296,23 +1137,20 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
       </c>
       <c r="H4">
         <v>19.07</v>
       </c>
       <c r="K4" t="s">
-        <v>245</v>
+        <v>193</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -1320,28 +1158,25 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
         <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
       </c>
       <c r="H5">
         <v>18.51</v>
       </c>
       <c r="K5" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="L5">
         <v>3</v>
@@ -1349,28 +1184,25 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
       </c>
       <c r="H6">
         <v>19.52</v>
       </c>
       <c r="K6" t="s">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -1378,22 +1210,19 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s">
         <v>22</v>
-      </c>
-      <c r="G7" t="s">
-        <v>26</v>
       </c>
       <c r="H7">
         <v>19.08</v>
@@ -1407,22 +1236,19 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H8">
         <v>18.35</v>
@@ -1430,80 +1256,71 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="D9" t="s">
-        <v>33</v>
-      </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H9">
         <v>19.1</v>
       </c>
       <c r="K9" t="s">
-        <v>251</v>
+        <v>198</v>
       </c>
       <c r="L9" t="s">
-        <v>252</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
-      <c r="D10" t="s">
-        <v>37</v>
-      </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H10">
         <v>19.33</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>254</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
       </c>
-      <c r="D11" t="s">
-        <v>41</v>
-      </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H11">
         <v>21.28</v>
@@ -1511,22 +1328,19 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" t="s">
-        <v>45</v>
-      </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="H12">
         <v>23.43</v>
@@ -1534,22 +1348,19 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
-      <c r="D13" t="s">
-        <v>50</v>
-      </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F13" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="H13">
         <v>24.02</v>
@@ -1557,22 +1368,22 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H14">
         <v>23.23</v>
@@ -1580,22 +1391,19 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
       </c>
-      <c r="D15" t="s">
-        <v>59</v>
-      </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="H15">
         <v>25.1</v>
@@ -1603,22 +1411,19 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
       </c>
-      <c r="D16" t="s">
-        <v>64</v>
-      </c>
       <c r="E16" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G16" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="H16">
         <v>24.84</v>
@@ -1626,22 +1431,19 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
-      <c r="D17" t="s">
-        <v>68</v>
-      </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H17">
         <v>23.5</v>
@@ -1649,22 +1451,19 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
-      <c r="D18" t="s">
-        <v>72</v>
-      </c>
       <c r="E18" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="H18">
         <v>25.21</v>
@@ -1672,22 +1471,19 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
-      <c r="D19" t="s">
-        <v>76</v>
-      </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H19">
         <v>23.35</v>
@@ -1695,22 +1491,19 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
-      <c r="D20" t="s">
-        <v>80</v>
-      </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="G20" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="H20">
         <v>24.11</v>
@@ -1718,22 +1511,19 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
       </c>
-      <c r="D21" t="s">
-        <v>84</v>
-      </c>
       <c r="E21" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="G21" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="H21">
         <v>24.32</v>
@@ -1741,22 +1531,19 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
       </c>
-      <c r="D22" t="s">
-        <v>88</v>
-      </c>
       <c r="E22" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="F22" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="G22" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H22">
         <v>23.42</v>
@@ -1764,22 +1551,19 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
       </c>
-      <c r="D23" t="s">
-        <v>92</v>
-      </c>
       <c r="E23" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="F23" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H23">
         <v>26.19</v>
@@ -1787,22 +1571,19 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
       </c>
-      <c r="D24" t="s">
-        <v>95</v>
-      </c>
       <c r="E24" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="F24" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="H24">
         <v>33.4</v>
@@ -1810,22 +1591,19 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
       </c>
-      <c r="D25" t="s">
-        <v>100</v>
-      </c>
       <c r="E25" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="F25" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="H25">
         <v>23.95</v>
@@ -1833,22 +1611,19 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
       </c>
-      <c r="D26" t="s">
-        <v>105</v>
-      </c>
       <c r="E26" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="F26" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="G26" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="H26">
         <v>28</v>
@@ -1856,22 +1631,19 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
-      <c r="D27" t="s">
-        <v>109</v>
-      </c>
       <c r="E27" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="F27" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="H27">
         <v>27.69</v>
@@ -1879,22 +1651,19 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
-      <c r="D28" t="s">
-        <v>114</v>
-      </c>
       <c r="E28" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="F28" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="G28" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="H28">
         <v>29.34</v>
@@ -1902,22 +1671,19 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
       </c>
-      <c r="D29" t="s">
-        <v>118</v>
-      </c>
       <c r="E29" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="F29" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="G29" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="H29">
         <v>27.69</v>
@@ -1925,22 +1691,19 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
       </c>
-      <c r="D30" t="s">
-        <v>122</v>
-      </c>
       <c r="E30" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="F30" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="G30" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="H30">
         <v>27.61</v>
@@ -1948,22 +1711,19 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
       </c>
-      <c r="D31" t="s">
-        <v>126</v>
-      </c>
       <c r="E31" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="F31" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="G31" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="H31">
         <v>27.68</v>
@@ -1971,22 +1731,19 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
-      <c r="D32" t="s">
-        <v>130</v>
-      </c>
       <c r="E32" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="F32" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="G32" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="H32">
         <v>24.32</v>
@@ -1994,22 +1751,19 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
       </c>
-      <c r="D33" t="s">
-        <v>134</v>
-      </c>
       <c r="E33" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="F33" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="G33" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="H33">
         <v>27.19</v>
@@ -2017,22 +1771,19 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
       </c>
-      <c r="D34" t="s">
-        <v>138</v>
-      </c>
       <c r="E34" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="F34" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="G34" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="H34">
         <v>28.07</v>
@@ -2040,22 +1791,19 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
       </c>
-      <c r="D35" t="s">
-        <v>143</v>
-      </c>
       <c r="E35" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="F35" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="G35" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="H35">
         <v>29.29</v>
@@ -2063,22 +1811,19 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
       </c>
-      <c r="D36" t="s">
-        <v>147</v>
-      </c>
       <c r="E36" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="F36" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="G36" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="H36">
         <v>34.86</v>
@@ -2086,22 +1831,19 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
       </c>
-      <c r="D37" t="s">
-        <v>151</v>
-      </c>
       <c r="E37" t="s">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="F37" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="G37" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="H37">
         <v>28.37</v>
@@ -2109,22 +1851,19 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="B38" t="s">
         <v>10</v>
       </c>
-      <c r="D38" t="s">
-        <v>155</v>
-      </c>
       <c r="E38" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="F38" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="G38" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="H38">
         <v>29.8</v>
@@ -2132,22 +1871,19 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="B39" t="s">
         <v>10</v>
       </c>
-      <c r="D39" t="s">
-        <v>159</v>
-      </c>
       <c r="E39" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F39" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="G39" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="H39">
         <v>35.32</v>
@@ -2155,22 +1891,19 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="B40" t="s">
         <v>10</v>
       </c>
-      <c r="D40" t="s">
-        <v>163</v>
-      </c>
       <c r="E40" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="F40" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="G40" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="H40">
         <v>34.06</v>
@@ -2178,22 +1911,22 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="F41" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="G41" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="H41">
         <v>27.38</v>
@@ -2201,22 +1934,19 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
       </c>
-      <c r="D42" t="s">
-        <v>170</v>
-      </c>
       <c r="E42" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="F42" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="G42" t="s">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="H42">
         <v>25.18</v>
@@ -2224,22 +1954,19 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
       </c>
-      <c r="D43" t="s">
-        <v>175</v>
-      </c>
       <c r="E43" t="s">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="F43" t="s">
-        <v>177</v>
+        <v>139</v>
       </c>
       <c r="G43" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="H43">
         <v>26.05</v>
@@ -2247,22 +1974,19 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
-      <c r="D44" t="s">
-        <v>180</v>
-      </c>
       <c r="E44" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="F44" t="s">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="G44" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="H44">
         <v>24.92</v>
@@ -2270,22 +1994,19 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>183</v>
+        <v>144</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
-      <c r="D45" t="s">
-        <v>184</v>
-      </c>
       <c r="E45" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="F45" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="G45" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="H45">
         <v>26.02</v>
@@ -2293,22 +2014,19 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
       </c>
-      <c r="D46" t="s">
-        <v>188</v>
-      </c>
       <c r="E46" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="F46" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="G46" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="H46">
         <v>28.62</v>
@@ -2316,22 +2034,19 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
       </c>
-      <c r="D47" t="s">
-        <v>192</v>
-      </c>
       <c r="E47" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="F47" t="s">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="G47" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="H47">
         <v>30.04</v>
@@ -2339,22 +2054,19 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
       </c>
-      <c r="D48" t="s">
-        <v>195</v>
-      </c>
       <c r="E48" t="s">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="F48" t="s">
-        <v>186</v>
+        <v>146</v>
       </c>
       <c r="G48" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="H48">
         <v>25.66</v>
@@ -2362,22 +2074,19 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="B49" t="s">
         <v>10</v>
       </c>
-      <c r="D49" t="s">
-        <v>198</v>
-      </c>
       <c r="E49" t="s">
-        <v>199</v>
+        <v>155</v>
       </c>
       <c r="F49" t="s">
-        <v>200</v>
+        <v>156</v>
       </c>
       <c r="G49" t="s">
-        <v>201</v>
+        <v>157</v>
       </c>
       <c r="H49">
         <v>35</v>
@@ -2385,22 +2094,22 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="B50" t="s">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="C50" t="s">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="E50" t="s">
-        <v>205</v>
+        <v>161</v>
       </c>
       <c r="F50" t="s">
-        <v>201</v>
+        <v>157</v>
       </c>
       <c r="G50" t="s">
-        <v>206</v>
+        <v>162</v>
       </c>
       <c r="H50">
         <v>51.56</v>
@@ -2408,22 +2117,22 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>207</v>
+        <v>163</v>
       </c>
       <c r="B51" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C51" t="s">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="E51" t="s">
-        <v>208</v>
+        <v>164</v>
       </c>
       <c r="F51" t="s">
-        <v>209</v>
+        <v>165</v>
       </c>
       <c r="G51" t="s">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="H51">
         <v>149.45</v>
@@ -2431,22 +2140,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>211</v>
+        <v>167</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
       </c>
-      <c r="D52" t="s">
-        <v>212</v>
-      </c>
       <c r="E52" t="s">
-        <v>213</v>
+        <v>168</v>
       </c>
       <c r="F52" t="s">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="G52" t="s">
-        <v>215</v>
+        <v>170</v>
       </c>
       <c r="H52">
         <v>24.1</v>
@@ -2454,22 +2160,19 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
       </c>
-      <c r="D53" t="s">
-        <v>217</v>
-      </c>
       <c r="E53" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="F53" t="s">
-        <v>215</v>
+        <v>170</v>
       </c>
       <c r="G53" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
       <c r="H53">
         <v>22.91</v>
@@ -2477,22 +2180,19 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
       </c>
-      <c r="D54" t="s">
-        <v>221</v>
-      </c>
       <c r="E54" t="s">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="F54" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
       <c r="G54" t="s">
-        <v>223</v>
+        <v>176</v>
       </c>
       <c r="H54">
         <v>23.04</v>
@@ -2500,22 +2200,19 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>224</v>
+        <v>177</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
       </c>
-      <c r="D55" t="s">
-        <v>225</v>
-      </c>
       <c r="E55" t="s">
-        <v>226</v>
+        <v>178</v>
       </c>
       <c r="F55" t="s">
-        <v>223</v>
+        <v>176</v>
       </c>
       <c r="G55" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
       <c r="H55">
         <v>22.74</v>
@@ -2523,22 +2220,19 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>228</v>
+        <v>180</v>
       </c>
       <c r="B56" t="s">
         <v>10</v>
       </c>
-      <c r="D56" t="s">
-        <v>229</v>
-      </c>
       <c r="E56" t="s">
-        <v>230</v>
+        <v>181</v>
       </c>
       <c r="F56" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
       <c r="G56" t="s">
-        <v>231</v>
+        <v>182</v>
       </c>
       <c r="H56">
         <v>22.74</v>
@@ -2546,22 +2240,19 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>183</v>
       </c>
       <c r="B57" t="s">
         <v>10</v>
       </c>
-      <c r="D57" t="s">
-        <v>233</v>
-      </c>
       <c r="E57" t="s">
-        <v>234</v>
+        <v>184</v>
       </c>
       <c r="F57" t="s">
-        <v>231</v>
+        <v>182</v>
       </c>
       <c r="G57" t="s">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="H57">
         <v>22.74</v>
@@ -2569,22 +2260,19 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>236</v>
+        <v>186</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
       </c>
-      <c r="D58" t="s">
-        <v>237</v>
-      </c>
       <c r="E58" t="s">
-        <v>238</v>
+        <v>187</v>
       </c>
       <c r="F58" t="s">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="G58" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="H58">
         <v>23.77</v>
@@ -2592,22 +2280,19 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>240</v>
+        <v>189</v>
       </c>
       <c r="B59" t="s">
         <v>10</v>
       </c>
-      <c r="D59" t="s">
-        <v>241</v>
-      </c>
       <c r="E59" t="s">
-        <v>242</v>
+        <v>190</v>
       </c>
       <c r="F59" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="G59" t="s">
-        <v>243</v>
+        <v>191</v>
       </c>
       <c r="H59">
         <v>22.33</v>
@@ -2615,22 +2300,22 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>244</v>
+        <v>192</v>
       </c>
       <c r="B60" t="s">
-        <v>245</v>
+        <v>193</v>
       </c>
       <c r="C60" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E60" t="s">
-        <v>246</v>
+        <v>194</v>
       </c>
       <c r="F60" t="s">
-        <v>243</v>
+        <v>191</v>
       </c>
       <c r="G60" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="H60">
         <v>22.38</v>
@@ -2638,22 +2323,19 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>247</v>
+        <v>195</v>
       </c>
       <c r="B61" t="s">
         <v>10</v>
       </c>
-      <c r="D61" t="s">
-        <v>248</v>
-      </c>
       <c r="E61" t="s">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c r="F61" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G61" t="s">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="H61">
         <v>21.53</v>
